--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.69292</v>
+        <v>17.20284</v>
       </c>
       <c r="D2" t="n">
-        <v>16.95551</v>
+        <v>16.59377</v>
       </c>
       <c r="E2" t="n">
-        <v>16.39853</v>
+        <v>16.82805</v>
       </c>
       <c r="F2" t="n">
-        <v>43.21704</v>
+        <v>43.08132</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05101</v>
+        <v>0.0509</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86529</v>
+        <v>1.80644</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.86604</v>
+        <v>17.20172</v>
       </c>
       <c r="D3" t="n">
-        <v>16.74981</v>
+        <v>16.62853</v>
       </c>
       <c r="E3" t="n">
-        <v>16.60724</v>
+        <v>17.09356</v>
       </c>
       <c r="F3" t="n">
-        <v>42.67337</v>
+        <v>42.96775</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05083</v>
+        <v>0.05121</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84773</v>
+        <v>1.83589</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.75533</v>
+        <v>16.8589</v>
       </c>
       <c r="D4" t="n">
-        <v>16.73497</v>
+        <v>16.40908</v>
       </c>
       <c r="E4" t="n">
-        <v>16.96547</v>
+        <v>16.77484</v>
       </c>
       <c r="F4" t="n">
-        <v>43.16266</v>
+        <v>43.10548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05128</v>
+        <v>0.05068</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81334</v>
+        <v>1.81423</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.0992</v>
+        <v>16.52252</v>
       </c>
       <c r="D6" t="n">
-        <v>15.98668</v>
+        <v>15.92088</v>
       </c>
       <c r="E6" t="n">
-        <v>16.52209</v>
+        <v>16.10899</v>
       </c>
       <c r="F6" t="n">
-        <v>22.05353</v>
+        <v>22.2659</v>
       </c>
       <c r="G6" t="n">
-        <v>34.4079</v>
+        <v>33.96654</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.55904</v>
+        <v>16.84152</v>
       </c>
       <c r="D7" t="n">
-        <v>16.26978</v>
+        <v>16.25307</v>
       </c>
       <c r="E7" t="n">
-        <v>16.42574</v>
+        <v>16.78072</v>
       </c>
       <c r="F7" t="n">
-        <v>22.41436</v>
+        <v>21.84121</v>
       </c>
       <c r="G7" t="n">
-        <v>34.57881</v>
+        <v>34.29129</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.89787</v>
+        <v>16.70247</v>
       </c>
       <c r="D8" t="n">
-        <v>16.11504</v>
+        <v>16.40593</v>
       </c>
       <c r="E8" t="n">
-        <v>16.45266</v>
+        <v>16.47676</v>
       </c>
       <c r="F8" t="n">
-        <v>21.5119</v>
+        <v>21.75337</v>
       </c>
       <c r="G8" t="n">
-        <v>34.36302</v>
+        <v>34.6783</v>
       </c>
     </row>
   </sheetData>
